--- a/w3-scd-effective-date-split/poc_v2/evidence/POC_v2_Evidence.xlsx
+++ b/w3-scd-effective-date-split/poc_v2/evidence/POC_v2_Evidence.xlsx
@@ -707,13 +707,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>209551</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>533401</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>108061</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -751,13 +751,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>598101</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>161926</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -795,13 +795,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>323851</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>32515</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -839,13 +839,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>295276</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>110552</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -883,13 +883,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>12961</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -927,13 +927,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>171451</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>69167</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -971,13 +971,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2914650</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>108994</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1015,13 +1015,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>171451</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>85726</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>523017</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1059,13 +1059,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>485525</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1103,13 +1103,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>438151</xdr:colOff>
-      <xdr:row>140</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>152401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1695451</xdr:colOff>
-      <xdr:row>150</xdr:row>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>84399</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1147,13 +1147,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>151</xdr:row>
+      <xdr:row>162</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1190625</xdr:colOff>
-      <xdr:row>162</xdr:row>
+      <xdr:row>173</xdr:row>
       <xdr:rowOff>116351</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1191,13 +1191,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>164</xdr:row>
+      <xdr:row>176</xdr:row>
       <xdr:rowOff>161926</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1704975</xdr:colOff>
-      <xdr:row>176</xdr:row>
+      <xdr:row>188</xdr:row>
       <xdr:rowOff>152336</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1235,13 +1235,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>200026</xdr:colOff>
-      <xdr:row>179</xdr:row>
+      <xdr:row>192</xdr:row>
       <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1752601</xdr:colOff>
-      <xdr:row>187</xdr:row>
+      <xdr:row>200</xdr:row>
       <xdr:rowOff>101547</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3056,7 +3056,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E65FD452-87F6-49C6-9D4C-F0918BC2BDFF}">
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.42578125" customWidth="1"/>
@@ -3093,88 +3093,179 @@
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target as day 1 left it — 3 rows, every one carrying B1, because day-1 SRC_2 held a single version covering the whole period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 1 output: 6 stage rows. RULE_NO shows 7, 13 and 17 firing; 2 rows retire (D), 4 insert (I). SK 101 produces nothing — rule 1, correctly untouched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One atomic MERGE applies all six: 4 inserted, 2 updated. ERROR_ON_NONDETERMINISTIC_MERGE stayed quiet — the multi-clause MERGE is valid Snowflake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target after: 7 rows. Both retirement mechanisms in one view — SK 102 by delete indicator (IS_DEL='Y', dates intact), SK 103 by dead record (expiry pulled back to 09-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re-run with the key still inside the window but nothing changed: Step 1 emits 0 stage rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERGE over an empty stage: 0 inserted, 0 updated. The apply is idempotent, not just the diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assertion PASS — stage 0, target still 7, live view still 5. Re-running costs nothing and changes nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B112" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C112" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D112" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="5" t="s">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B113" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C113" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D113" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC_2 changes exactly on a boundary SRC_1 already uses, so no new interval appears: 1 insert, 1 update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rule 9 proven: SK 103 becomes a dead record (09-21 → 09-21) and SK 401 carries B9 forward. SK 101 and 102 untouched — rules 1 and 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B146" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C146" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D146" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="5" t="s">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B138" s="8" t="s">
+      <c r="B147" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C147" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D138" s="8" t="s">
+      <c r="D147" s="8" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC_1 seeded with one clean version of K1 running to the high end date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SRC_2 seeded with a deliberately corrupt row — NULL business key — alongside the valid K1 row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MERGE writes nothing: 0 inserted, 0 updated. The NULL key never reaches the stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Target unchanged at 1 row. The corrupt row is dropped SILENTLY — nothing errors and nothing is logged. The check belongs upstream.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/w3-scd-effective-date-split/poc_v2/evidence/POC_v2_Evidence.xlsx
+++ b/w3-scd-effective-date-split/poc_v2/evidence/POC_v2_Evidence.xlsx
@@ -3623,7 +3623,7 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>random keys at scale, compared row for row against tools/verify.py</t>
+          <t>many keys of different shapes at once, checked against structural invariants</t>
         </is>
       </c>
       <c r="E96" s="9" t="inlineStr"/>
